--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 601.254,27</t>
-  </si>
-  <si>
-    <t>R$ 3.267,69
-R$ 3.339,21</t>
-  </si>
-  <si>
-    <t>8.6%
-11.0%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 604.009,99</t>
+  </si>
+  <si>
+    <t>R$ 3.264,92
+R$ 3.335,88</t>
+  </si>
+  <si>
+    <t>8.8%
+11.1%</t>
   </si>
   <si>
     <t>37.4</t>
   </si>
   <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>(4.9%)</t>
-  </si>
-  <si>
-    <t>(52.0%)</t>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>(4.8%)</t>
+  </si>
+  <si>
+    <t>(51.9%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -956,7 +956,7 @@
     <t>10.8%</t>
   </si>
   <si>
-    <t>4.8</t>
+    <t>4.9</t>
   </si>
   <si>
     <t>7.7</t>
@@ -968,13 +968,13 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>71.8%</t>
+    <t>71.9%</t>
   </si>
   <si>
     <t>-R$ 22.938,42</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -6650,7 +6650,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6686,25 +6686,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>2755.7199999999998</v>
+      </c>
+      <c r="P42" s="5">
+        <v>2755.7199999999998</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.67087256786335758</v>
+      </c>
+      <c r="R42" s="7">
+        <v>34</v>
+      </c>
+      <c r="S42" s="6">
+        <v>1</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.1591194678704658</v>
+      </c>
+      <c r="U42" s="6">
+        <v>-0.16250609641037553</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.057996095394307119</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0057810662912052028</v>
+      </c>
+      <c r="X42" s="8">
+        <v>24.384720833333333</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>5.2371428571428575</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>6.4022727272727273</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>12.275188</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>18.518054166666666</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.83333333333333337</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -20735,7 +20771,7 @@
         <v>-1149.8</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">

--- a/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
+++ b/novo projeto/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-14).xlsx
@@ -912,21 +912,21 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 604.009,99</t>
-  </si>
-  <si>
-    <t>R$ 3.264,92
-R$ 3.335,88</t>
-  </si>
-  <si>
-    <t>8.8%
-11.1%</t>
+176</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R$ 607.203,18</t>
+  </si>
+  <si>
+    <t>R$ 3.264,53
+R$ 3.335,07</t>
+  </si>
+  <si>
+    <t>8.9%
+11.2%</t>
   </si>
   <si>
     <t>37.4</t>
@@ -935,10 +935,10 @@
     <t>3.1%</t>
   </si>
   <si>
-    <t>(4.8%)</t>
-  </si>
-  <si>
-    <t>(51.9%)</t>
+    <t>(4.7%)</t>
+  </si>
+  <si>
+    <t>(51.7%)</t>
   </si>
   <si>
     <t>4.3%</t>
@@ -947,16 +947,16 @@
     <t>(0.1%)</t>
   </si>
   <si>
-    <t>27.6</t>
-  </si>
-  <si>
-    <t>69.5%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>4.9</t>
+    <t>27.5</t>
+  </si>
+  <si>
+    <t>69.2%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>4.8</t>
   </si>
   <si>
     <t>7.7</t>
@@ -968,13 +968,13 @@
     <t>19.1</t>
   </si>
   <si>
-    <t>71.9%</t>
+    <t>72.0%</t>
   </si>
   <si>
     <t>-R$ 22.938,42</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>2.95</t>
   </si>
   <si>
     <t>3.52</t>
@@ -8698,7 +8698,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>44</v>
@@ -8734,25 +8734,61 @@
       <c t="s" r="N58" s="4">
         <v>52</v>
       </c>
-      <c r="O58" s="5"/>
-      <c r="P58" s="5"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="7"/>
-      <c r="S58" s="6"/>
-      <c r="T58" s="6"/>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-      <c r="X58" s="8"/>
-      <c r="Y58" s="6"/>
-      <c r="Z58" s="6"/>
-      <c r="AA58" s="8"/>
-      <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
-      <c r="AD58" s="8"/>
-      <c r="AE58" s="6"/>
+      <c r="O58" s="5">
+        <v>3193.1900000000001</v>
+      </c>
+      <c r="P58" s="5">
+        <v>3193.1900000000001</v>
+      </c>
+      <c r="Q58" s="6">
+        <v>0.1958438192821621</v>
+      </c>
+      <c r="R58" s="7">
+        <v>37</v>
+      </c>
+      <c r="S58" s="6">
+        <v>-0.026315789473684181</v>
+      </c>
+      <c r="T58" s="6">
+        <v>0.13909353968915097</v>
+      </c>
+      <c r="U58" s="6">
+        <v>-0.22379435611410531</v>
+      </c>
+      <c r="V58" s="6">
+        <v>0.016863074229845391</v>
+      </c>
+      <c r="W58" s="6">
+        <v>-0.0077298876671917423</v>
+      </c>
+      <c r="X58" s="8">
+        <v>24.339705882352941</v>
+      </c>
+      <c r="Y58" s="6">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="Z58" s="6">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA58" s="8">
+        <v>3.3421052631578947</v>
+      </c>
+      <c r="AB58" s="8">
+        <v>7.3916676470588234</v>
+      </c>
+      <c r="AC58" s="8">
+        <v>10.641176</v>
+      </c>
+      <c r="AD58" s="8">
+        <v>17.541667647058823</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>0.8529411764705882</v>
+      </c>
       <c r="AF58" s="9"/>
-      <c r="AG58" s="5"/>
+      <c r="AG58" s="5">
+        <v>0</v>
+      </c>
       <c r="AH58" s="10">
         <v>2</v>
       </c>
@@ -15381,7 +15417,9 @@
       <c r="AB111" s="8">
         <v>2.3166666666666669</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>9.1944429999999997</v>
+      </c>
       <c r="AD111" s="8">
         <v>16.161100000000001</v>
       </c>
@@ -16883,7 +16921,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17276,7 +17314,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18453,7 +18491,7 @@
         <v>-41.899999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -21983,7 +22021,7 @@
         <v>-923.55999999999995</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28110,7 +28148,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
